--- a/LoanOfficer-A/2023/80 haobijam joyshree.xlsx
+++ b/LoanOfficer-A/2023/80 haobijam joyshree.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>300</v>
+        <v>3900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>35700</v>
+        <v>32100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -883,9 +883,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C4" s="4">
+        <v>300</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -909,9 +915,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C5" s="4">
+        <v>300</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -935,9 +947,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C6" s="4">
+        <v>300</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -961,9 +979,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C7" s="4">
+        <v>300</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -987,9 +1011,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C8" s="4">
+        <v>300</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1013,9 +1043,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C9" s="4">
+        <v>300</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1039,9 +1075,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C10" s="4">
+        <v>300</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1065,9 +1107,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C11" s="4">
+        <v>300</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1091,9 +1139,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C12" s="4">
+        <v>300</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1117,9 +1171,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C13" s="4">
+        <v>300</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1143,9 +1203,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C14" s="4">
+        <v>300</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1169,9 +1235,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C15" s="4">
+        <v>300</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/80 haobijam joyshree.xlsx
+++ b/LoanOfficer-A/2023/80 haobijam joyshree.xlsx
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3900</v>
+        <v>9000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>32100</v>
+        <v>27000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1267,9 +1267,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C16" s="4">
+        <v>300</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1293,9 +1299,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C17" s="4">
+        <v>300</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1319,9 +1331,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C18" s="4">
+        <v>300</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1345,9 +1363,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C19" s="4">
+        <v>300</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1371,9 +1395,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C20" s="4">
+        <v>300</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1397,9 +1427,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C21" s="4">
+        <v>300</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1423,9 +1459,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C22" s="4">
+        <v>300</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1449,9 +1491,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C23" s="4">
+        <v>300</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1475,9 +1523,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C24" s="4">
+        <v>300</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1501,9 +1555,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C25" s="4">
+        <v>300</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1527,9 +1587,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C26" s="4">
+        <v>300</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1553,9 +1619,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C27" s="4">
+        <v>300</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1579,9 +1651,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C28" s="4">
+        <v>300</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1605,9 +1683,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C29" s="4">
+        <v>300</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1631,9 +1715,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C30" s="4">
+        <v>300</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1657,9 +1747,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C31" s="4">
+        <v>300</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1683,9 +1779,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C32" s="4">
+        <v>300</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>
